--- a/Output/summary_OMOP_tables.xlsx
+++ b/Output/summary_OMOP_tables.xlsx
@@ -378,7 +378,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>niakhar_hdss_cdm</t>
+          <t>meiru_karonga_hdss_cdm</t>
         </is>
       </c>
       <c r="B2">
@@ -388,7 +388,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ouagadougou_hdss_cdm</t>
+          <t>niakhar_hdss_cdm</t>
         </is>
       </c>
       <c r="B3">
@@ -398,21 +398,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nuhdss_cdm</t>
+          <t>ouagadougou_hdss_cdm</t>
         </is>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>meiru_cdm</t>
+          <t>nuhdss_cdm</t>
         </is>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -460,41 +460,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>niakhar_hdss_cdm</t>
+          <t>meiru_karonga_hdss_cdm</t>
         </is>
       </c>
       <c r="B2">
-        <v>4043</v>
+        <v>4645</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ouagadougou_hdss_cdm</t>
+          <t>niakhar_hdss_cdm</t>
         </is>
       </c>
       <c r="B3">
-        <v>3274</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nuhdss_cdm</t>
+          <t>ouagadougou_hdss_cdm</t>
         </is>
       </c>
       <c r="B4">
-        <v>5493</v>
+        <v>3274</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>meiru_cdm</t>
+          <t>nuhdss_cdm</t>
         </is>
       </c>
       <c r="B5">
-        <v>4645</v>
+        <v>5493</v>
       </c>
     </row>
     <row r="6">
@@ -542,7 +542,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>niakhar_hdss_cdm</t>
+          <t>meiru_karonga_hdss_cdm</t>
         </is>
       </c>
       <c r="B2">
@@ -552,7 +552,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ouagadougou_hdss_cdm</t>
+          <t>niakhar_hdss_cdm</t>
         </is>
       </c>
       <c r="B3">
@@ -562,7 +562,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nuhdss_cdm</t>
+          <t>ouagadougou_hdss_cdm</t>
         </is>
       </c>
       <c r="B4">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>meiru_cdm</t>
+          <t>nuhdss_cdm</t>
         </is>
       </c>
       <c r="B5">
@@ -624,41 +624,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>niakhar_hdss_cdm</t>
+          <t>meiru_karonga_hdss_cdm</t>
         </is>
       </c>
       <c r="B2">
-        <v>4225</v>
+        <v>4645</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ouagadougou_hdss_cdm</t>
+          <t>niakhar_hdss_cdm</t>
         </is>
       </c>
       <c r="B3">
-        <v>4345</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nuhdss_cdm</t>
+          <t>ouagadougou_hdss_cdm</t>
         </is>
       </c>
       <c r="B4">
-        <v>6216</v>
+        <v>4345</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>meiru_cdm</t>
+          <t>nuhdss_cdm</t>
         </is>
       </c>
       <c r="B5">
-        <v>4645</v>
+        <v>6216</v>
       </c>
     </row>
     <row r="6">
@@ -706,7 +706,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>niakhar_hdss_cdm</t>
+          <t>meiru_karonga_hdss_cdm</t>
         </is>
       </c>
       <c r="B2">
@@ -716,7 +716,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ouagadougou_hdss_cdm</t>
+          <t>niakhar_hdss_cdm</t>
         </is>
       </c>
       <c r="B3">
@@ -726,21 +726,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nuhdss_cdm</t>
+          <t>ouagadougou_hdss_cdm</t>
         </is>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>meiru_cdm</t>
+          <t>nuhdss_cdm</t>
         </is>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -788,41 +788,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>niakhar_hdss_cdm</t>
+          <t>meiru_karonga_hdss_cdm</t>
         </is>
       </c>
       <c r="B2">
-        <v>4043</v>
+        <v>13394</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ouagadougou_hdss_cdm</t>
+          <t>niakhar_hdss_cdm</t>
         </is>
       </c>
       <c r="B3">
-        <v>3274</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nuhdss_cdm</t>
+          <t>ouagadougou_hdss_cdm</t>
         </is>
       </c>
       <c r="B4">
-        <v>5493</v>
+        <v>3274</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>meiru_cdm</t>
+          <t>nuhdss_cdm</t>
         </is>
       </c>
       <c r="B5">
-        <v>13394</v>
+        <v>5493</v>
       </c>
     </row>
     <row r="6">
@@ -870,41 +870,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>niakhar_hdss_cdm</t>
+          <t>meiru_karonga_hdss_cdm</t>
         </is>
       </c>
       <c r="B2">
-        <v>4043</v>
+        <v>4645</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ouagadougou_hdss_cdm</t>
+          <t>niakhar_hdss_cdm</t>
         </is>
       </c>
       <c r="B3">
-        <v>3274</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nuhdss_cdm</t>
+          <t>ouagadougou_hdss_cdm</t>
         </is>
       </c>
       <c r="B4">
-        <v>5493</v>
+        <v>3274</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>meiru_cdm</t>
+          <t>nuhdss_cdm</t>
         </is>
       </c>
       <c r="B5">
-        <v>4645</v>
+        <v>5493</v>
       </c>
     </row>
     <row r="6">
@@ -952,41 +952,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>niakhar_hdss_cdm</t>
+          <t>meiru_karonga_hdss_cdm</t>
         </is>
       </c>
       <c r="B2">
-        <v>4226</v>
+        <v>4645</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ouagadougou_hdss_cdm</t>
+          <t>niakhar_hdss_cdm</t>
         </is>
       </c>
       <c r="B3">
-        <v>4345</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nuhdss_cdm</t>
+          <t>ouagadougou_hdss_cdm</t>
         </is>
       </c>
       <c r="B4">
-        <v>6217</v>
+        <v>4345</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>meiru_cdm</t>
+          <t>nuhdss_cdm</t>
         </is>
       </c>
       <c r="B5">
-        <v>4645</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="6">
@@ -1034,7 +1034,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>niakhar_hdss_cdm</t>
+          <t>meiru_karonga_hdss_cdm</t>
         </is>
       </c>
       <c r="B2">
@@ -1044,7 +1044,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ouagadougou_hdss_cdm</t>
+          <t>niakhar_hdss_cdm</t>
         </is>
       </c>
       <c r="B3">
@@ -1054,21 +1054,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nuhdss_cdm</t>
+          <t>ouagadougou_hdss_cdm</t>
         </is>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>meiru_cdm</t>
+          <t>nuhdss_cdm</t>
         </is>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1116,41 +1116,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>niakhar_hdss_cdm</t>
+          <t>meiru_karonga_hdss_cdm</t>
         </is>
       </c>
       <c r="B2">
-        <v>4043</v>
+        <v>4645</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ouagadougou_hdss_cdm</t>
+          <t>niakhar_hdss_cdm</t>
         </is>
       </c>
       <c r="B3">
-        <v>3274</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nuhdss_cdm</t>
+          <t>ouagadougou_hdss_cdm</t>
         </is>
       </c>
       <c r="B4">
-        <v>5493</v>
+        <v>3274</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>meiru_cdm</t>
+          <t>nuhdss_cdm</t>
         </is>
       </c>
       <c r="B5">
-        <v>4645</v>
+        <v>5493</v>
       </c>
     </row>
     <row r="6">
